--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post FET_HRM-2031-0132/Panel 02/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post FET_HRM-2031-0132/Panel 02/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.57302</v>
+        <v>16.63501</v>
       </c>
       <c r="D2" t="n">
-        <v>16.82333</v>
+        <v>16.54861</v>
       </c>
       <c r="E2" t="n">
-        <v>16.87825</v>
+        <v>16.60282</v>
       </c>
       <c r="F2" t="n">
-        <v>42.17027</v>
+        <v>43.09936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05019</v>
+        <v>0.05093</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82478</v>
+        <v>1.87768</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.82329</v>
+        <v>16.89939</v>
       </c>
       <c r="D3" t="n">
-        <v>16.28726</v>
+        <v>16.63363</v>
       </c>
       <c r="E3" t="n">
-        <v>16.78016</v>
+        <v>16.80848</v>
       </c>
       <c r="F3" t="n">
-        <v>41.27108</v>
+        <v>42.74757</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05112</v>
+        <v>0.04971</v>
       </c>
       <c r="H3" t="n">
-        <v>1.78746</v>
+        <v>1.83763</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.19096</v>
+        <v>16.76267</v>
       </c>
       <c r="D4" t="n">
-        <v>16.40123</v>
+        <v>16.22225</v>
       </c>
       <c r="E4" t="n">
-        <v>16.7262</v>
+        <v>16.70159</v>
       </c>
       <c r="F4" t="n">
-        <v>42.90241</v>
+        <v>41.93013</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04997</v>
+        <v>0.05157</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85543</v>
+        <v>1.8272</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.50281</v>
+        <v>16.80115</v>
       </c>
       <c r="D6" t="n">
-        <v>15.94317</v>
+        <v>16.09017</v>
       </c>
       <c r="E6" t="n">
-        <v>16.33255</v>
+        <v>16.2068</v>
       </c>
       <c r="F6" t="n">
-        <v>22.06277</v>
+        <v>21.91183</v>
       </c>
       <c r="G6" t="n">
-        <v>34.42859</v>
+        <v>33.84164</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.21208</v>
+        <v>16.66884</v>
       </c>
       <c r="D7" t="n">
-        <v>15.83201</v>
+        <v>16.33048</v>
       </c>
       <c r="E7" t="n">
-        <v>16.60349</v>
+        <v>16.38174</v>
       </c>
       <c r="F7" t="n">
-        <v>22.02042</v>
+        <v>21.73139</v>
       </c>
       <c r="G7" t="n">
-        <v>34.40161</v>
+        <v>33.91638</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.40305</v>
+        <v>16.75091</v>
       </c>
       <c r="D8" t="n">
-        <v>16.1303</v>
+        <v>16.26678</v>
       </c>
       <c r="E8" t="n">
-        <v>16.35875</v>
+        <v>16.61223</v>
       </c>
       <c r="F8" t="n">
-        <v>21.89537</v>
+        <v>21.75769</v>
       </c>
       <c r="G8" t="n">
-        <v>33.23103</v>
+        <v>34.60511</v>
       </c>
     </row>
   </sheetData>
